--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.62124409196677</v>
+        <v>5.138452164944599</v>
       </c>
       <c r="D2" t="n">
-        <v>26.55467616910967</v>
+        <v>4.315134877480321</v>
       </c>
       <c r="E2" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F2" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.59465629420691</v>
+        <v>4.484131647808623</v>
       </c>
       <c r="D3" t="n">
-        <v>27.94981628304018</v>
+        <v>4.541845145994029</v>
       </c>
       <c r="E3" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F3" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.1174624443882</v>
+        <v>3.756587647213082</v>
       </c>
       <c r="D4" t="n">
-        <v>29.33884389506393</v>
+        <v>4.767562132947889</v>
       </c>
       <c r="E4" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F4" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.53180536242747</v>
+        <v>5.286418371394464</v>
       </c>
       <c r="D5" t="n">
-        <v>37.88272353898056</v>
+        <v>6.155942575084341</v>
       </c>
       <c r="E5" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F5" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.08046820522296</v>
+        <v>6.675576083348731</v>
       </c>
       <c r="D6" t="n">
-        <v>34.2053225464656</v>
+        <v>5.558364913800659</v>
       </c>
       <c r="E6" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F6" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.1666249619165</v>
+        <v>4.902076556311431</v>
       </c>
       <c r="D7" t="n">
-        <v>27.93593561733127</v>
+        <v>4.539589537816331</v>
       </c>
       <c r="E7" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F7" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.05878025841827</v>
+        <v>2.772051791992969</v>
       </c>
       <c r="D8" t="n">
-        <v>26.26500251822126</v>
+        <v>4.268062909210955</v>
       </c>
       <c r="E8" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F8" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.14970676675269</v>
+        <v>7.661827349597313</v>
       </c>
       <c r="D9" t="n">
-        <v>7.178188680734626</v>
+        <v>1.166455660619377</v>
       </c>
       <c r="E9" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F9" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.22651924229873</v>
+        <v>8.324309376873543</v>
       </c>
       <c r="D10" t="n">
-        <v>7.107999423475401</v>
+        <v>1.155049906314753</v>
       </c>
       <c r="E10" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F10" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>60.86583531458468</v>
+        <v>9.890698238620011</v>
       </c>
       <c r="D11" t="n">
-        <v>21.07627396825915</v>
+        <v>3.424894519842112</v>
       </c>
       <c r="E11" t="n">
-        <v>12.88530554306084</v>
+        <v>2.093862150747386</v>
       </c>
       <c r="F11" t="n">
-        <v>9.705529607822823</v>
+        <v>1.577148561271209</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
